--- a/corr_matrix/residual_exam3B_3PL.xlsx
+++ b/corr_matrix/residual_exam3B_3PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>3B01</t>
@@ -525,52 +530,52 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2633623971653209</v>
+        <v>0.2633463200130575</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2996253768485736</v>
+        <v>-0.2996681907014985</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2482729988930325</v>
+        <v>-0.2483151663060719</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1488451299941777</v>
+        <v>-0.1488409589258924</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1357547671856076</v>
+        <v>-0.1357547085501097</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1227782444892338</v>
+        <v>-0.1227809082321726</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01530107582543403</v>
+        <v>0.0152969466512487</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5115974629762482</v>
+        <v>0.5116153949227948</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2963049211988252</v>
+        <v>-0.2963194267793881</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3296227219838192</v>
+        <v>0.3296222593566802</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2425642125527341</v>
+        <v>0.2425669914484055</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1052868472941573</v>
+        <v>0.1052749905785</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3025224302472294</v>
+        <v>-0.3025414086752497</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1480481308387691</v>
+        <v>-0.1480280602383607</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.01966628653205298</v>
+        <v>-0.01964295660280319</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1315149064270793</v>
+        <v>0.1315126204634179</v>
       </c>
     </row>
     <row r="3">
@@ -580,55 +585,55 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2633623971653209</v>
+        <v>0.2633463200130575</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1463223696467953</v>
+        <v>-0.1463473679637778</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2018191151629042</v>
+        <v>0.2017982418917784</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1186990397292863</v>
+        <v>-0.1187124869164489</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03371590971180102</v>
+        <v>0.03370588675345117</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01132782372976669</v>
+        <v>0.01131517104924295</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07559664690921278</v>
+        <v>0.07559728552238235</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.009954509170816479</v>
+        <v>-0.009958638658091443</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.07487169789726761</v>
+        <v>-0.07488420500260019</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3229686235462816</v>
+        <v>-0.3229787372599275</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09606960732462316</v>
+        <v>0.09606193197988995</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1449202013617249</v>
+        <v>0.1449056711565395</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1285168737087633</v>
+        <v>0.1284994890650402</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.228424999538051</v>
+        <v>-0.2284251428394521</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1666239735273201</v>
+        <v>-0.1666287345046819</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2916657504417445</v>
+        <v>-0.2916707537545707</v>
       </c>
     </row>
     <row r="4">
@@ -638,55 +643,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2996253768485736</v>
+        <v>-0.2996681907014985</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1463223696467953</v>
+        <v>-0.1463473679637778</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5236412179600067</v>
+        <v>0.5236201821152033</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.07361423395296955</v>
+        <v>-0.07363305043296703</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2289426607343401</v>
+        <v>0.2289339001127322</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07166229679853929</v>
+        <v>-0.07168047132475694</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07585109143636357</v>
+        <v>0.07585198186848036</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3562892381485438</v>
+        <v>-0.3563009164935205</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1475766388401387</v>
+        <v>-0.1475976621141215</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1863211507765748</v>
+        <v>-0.1863342429855226</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.09337776036899126</v>
+        <v>-0.09339287793660783</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2206497750422585</v>
+        <v>0.2206286299208816</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2191235361737836</v>
+        <v>0.2190993836510087</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.08859419723550245</v>
+        <v>-0.08859948004689602</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2463175713112158</v>
+        <v>-0.2463249298705208</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.153015896914925</v>
+        <v>-0.1530279760886197</v>
       </c>
     </row>
     <row r="5">
@@ -696,55 +701,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2482729988930325</v>
+        <v>-0.2483151663060719</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2018191151629042</v>
+        <v>0.2017982418917784</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5236412179600067</v>
+        <v>0.5236201821152033</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1145331602203963</v>
+        <v>-0.114545064057309</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.01449720222478054</v>
+        <v>-0.01450604479509847</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2331842828834325</v>
+        <v>-0.2332031014536264</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04825730489346786</v>
+        <v>0.04825663448456807</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2880937465377374</v>
+        <v>-0.2880974968522592</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07104115812971837</v>
+        <v>0.07102166423725503</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2592267895176368</v>
+        <v>-0.2592428771711739</v>
       </c>
       <c r="M5" t="n">
-        <v>0.208997325825457</v>
+        <v>0.2089903989017465</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01880500660357181</v>
+        <v>0.01877999711509601</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08617151389480943</v>
+        <v>0.08614156464175782</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2658783583518063</v>
+        <v>-0.2658841969949202</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1026547546344741</v>
+        <v>-0.102650397078287</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.09448008372799722</v>
+        <v>-0.09448757927052656</v>
       </c>
     </row>
     <row r="6">
@@ -754,55 +759,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1488451299941777</v>
+        <v>-0.1488409589258924</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1186990397292863</v>
+        <v>-0.1187124869164489</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.07361423395296955</v>
+        <v>-0.07363305043296703</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1145331602203963</v>
+        <v>-0.114545064057309</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.01665375165320526</v>
+        <v>-0.01665137204047982</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2107042448915069</v>
+        <v>0.2107155558160763</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01460942567558167</v>
+        <v>0.01460412309276109</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2665299763919145</v>
+        <v>-0.2665133288161204</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1141077676108638</v>
+        <v>-0.1141039853558811</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2335665364432838</v>
+        <v>-0.2335651178478877</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2890011193574685</v>
+        <v>-0.2889993477990974</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.09714522530321366</v>
+        <v>-0.09714803839489827</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1100201902094372</v>
+        <v>-0.1100246532969607</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.09953736872705168</v>
+        <v>-0.09952899762682288</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1406992796417736</v>
+        <v>-0.1406890859728792</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06905742037009066</v>
+        <v>0.06906645850482386</v>
       </c>
     </row>
     <row r="7">
@@ -812,55 +817,55 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1357547671856076</v>
+        <v>-0.1357547085501097</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03371590971180102</v>
+        <v>0.03370588675345117</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2289426607343401</v>
+        <v>0.2289339001127322</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01449720222478054</v>
+        <v>-0.01450604479509847</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01665375165320526</v>
+        <v>-0.01665137204047982</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09879646111929266</v>
+        <v>0.09879576737220674</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1780266959760035</v>
+        <v>-0.1780271781586087</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1434095713554527</v>
+        <v>-0.1434001886753894</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1005234283544508</v>
+        <v>-0.1005169029078608</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1845924557059135</v>
+        <v>-0.1845943706305788</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1046250086772224</v>
+        <v>-0.1046317042787256</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01808750149745618</v>
+        <v>-0.01809581323940824</v>
       </c>
       <c r="O7" t="n">
-        <v>0.09742786136531222</v>
+        <v>0.09742116197334463</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.231597346161858</v>
+        <v>-0.2315950880609488</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.05648179332423926</v>
+        <v>-0.0564805618575122</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1526114212996356</v>
+        <v>-0.1526104192842474</v>
       </c>
     </row>
     <row r="8">
@@ -870,55 +875,55 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1227782444892338</v>
+        <v>-0.1227809082321726</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01132782372976669</v>
+        <v>0.01131517104924295</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07166229679853929</v>
+        <v>-0.07168047132475694</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2331842828834325</v>
+        <v>-0.2332031014536264</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2107042448915069</v>
+        <v>0.2107155558160763</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09879646111929266</v>
+        <v>0.09879576737220674</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04657998238162203</v>
+        <v>0.04657895808208456</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1113026901411805</v>
+        <v>-0.1112868790756474</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.110984989688466</v>
+        <v>-0.1109774696738625</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.08420634657215011</v>
+        <v>-0.08420510935998457</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3139904894573305</v>
+        <v>-0.3139946528886671</v>
       </c>
       <c r="N8" t="n">
-        <v>0.06963663455052918</v>
+        <v>0.06963366271904832</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.05810370347223572</v>
+        <v>-0.05810826328302209</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1083133964638782</v>
+        <v>-0.1083083749550653</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1683131366924297</v>
+        <v>-0.1683028290656185</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002501461894858713</v>
+        <v>0.002509791409928436</v>
       </c>
     </row>
     <row r="9">
@@ -928,55 +933,55 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01530107582543403</v>
+        <v>0.0152969466512487</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07559664690921278</v>
+        <v>0.07559728552238235</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07585109143636357</v>
+        <v>0.07585198186848036</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04825730489346786</v>
+        <v>0.04825663448456807</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01460942567558167</v>
+        <v>0.01460412309276109</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1780266959760035</v>
+        <v>-0.1780271781586087</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04657998238162203</v>
+        <v>0.04657895808208456</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2526848867661798</v>
+        <v>-0.2526828134434778</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1187760721653451</v>
+        <v>-0.1187846618456213</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1984950831030369</v>
+        <v>-0.1984951371814229</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1290846563163097</v>
+        <v>-0.1290846440590424</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04784530745402252</v>
+        <v>-0.04784660071458123</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1517051060556925</v>
+        <v>0.1517038804515338</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1042482409667988</v>
+        <v>-0.1042472562139691</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1779438451389138</v>
+        <v>-0.1779433193663462</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1208143663468068</v>
+        <v>0.1208124555009644</v>
       </c>
     </row>
     <row r="10">
@@ -986,55 +991,55 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5115974629762482</v>
+        <v>0.5116153949227948</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.009954509170816479</v>
+        <v>-0.009958638658091443</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3562892381485438</v>
+        <v>-0.3563009164935205</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2880937465377374</v>
+        <v>-0.2880974968522592</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2665299763919145</v>
+        <v>-0.2665133288161204</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1434095713554527</v>
+        <v>-0.1434001886753894</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1113026901411805</v>
+        <v>-0.1112868790756474</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2526848867661798</v>
+        <v>-0.2526828134434778</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.03279140354953321</v>
+        <v>-0.03279209900960602</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3131214223669063</v>
+        <v>0.3131252630104621</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1994498865317438</v>
+        <v>0.1994548436741225</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1560413107893932</v>
+        <v>0.1560476141303379</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4014707216967044</v>
+        <v>-0.4014672440405158</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01137560382530292</v>
+        <v>0.01139122932632961</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1801940201260942</v>
+        <v>0.1802086516815085</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.06673731860917852</v>
+        <v>-0.0667163486895082</v>
       </c>
     </row>
     <row r="11">
@@ -1044,55 +1049,55 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2963049211988252</v>
+        <v>-0.2963194267793881</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.07487169789726761</v>
+        <v>-0.07488420500260019</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1475766388401387</v>
+        <v>-0.1475976621141215</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07104115812971837</v>
+        <v>0.07102166423725503</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1141077676108638</v>
+        <v>-0.1141039853558811</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1005234283544508</v>
+        <v>-0.1005169029078608</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.110984989688466</v>
+        <v>-0.1109774696738625</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1187760721653451</v>
+        <v>-0.1187846618456213</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.03279140354953321</v>
+        <v>-0.03279209900960602</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.07077011084197735</v>
+        <v>-0.07077199820971503</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1089522674104774</v>
+        <v>-0.1089466401285601</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1801872919912418</v>
+        <v>-0.1801874470417569</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2110717045254923</v>
+        <v>-0.211076096741468</v>
       </c>
       <c r="P11" t="n">
-        <v>0.04595707700570791</v>
+        <v>0.04596758191039343</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001108510895196234</v>
+        <v>0.001119136990765943</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.08631534911131751</v>
+        <v>-0.08630211861237901</v>
       </c>
     </row>
     <row r="12">
@@ -1102,55 +1107,55 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3296227219838192</v>
+        <v>0.3296222593566802</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3229686235462816</v>
+        <v>-0.3229787372599275</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1863211507765748</v>
+        <v>-0.1863342429855226</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2592267895176368</v>
+        <v>-0.2592428771711739</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2335665364432838</v>
+        <v>-0.2335651178478877</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1845924557059135</v>
+        <v>-0.1845943706305788</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.08420634657215011</v>
+        <v>-0.08420510935998457</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1984950831030369</v>
+        <v>-0.1984951371814229</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3131214223669063</v>
+        <v>0.3131252630104621</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.07077011084197735</v>
+        <v>-0.07077199820971503</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2445675139367825</v>
+        <v>0.2445669171278733</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1311758439470698</v>
+        <v>-0.1311790209937747</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1290069085299771</v>
+        <v>-0.1290135262247127</v>
       </c>
       <c r="P12" t="n">
-        <v>0.06537238530367127</v>
+        <v>0.06537804670182855</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1445407681560441</v>
+        <v>0.1445446068592358</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.01757525324315103</v>
+        <v>-0.0175686449599894</v>
       </c>
     </row>
     <row r="13">
@@ -1160,55 +1165,55 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2425642125527341</v>
+        <v>0.2425669914484055</v>
       </c>
       <c r="C13" t="n">
-        <v>0.09606960732462316</v>
+        <v>0.09606193197988995</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.09337776036899126</v>
+        <v>-0.09339287793660783</v>
       </c>
       <c r="E13" t="n">
-        <v>0.208997325825457</v>
+        <v>0.2089903989017465</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2890011193574685</v>
+        <v>-0.2889993477990974</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1046250086772224</v>
+        <v>-0.1046317042787256</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3139904894573305</v>
+        <v>-0.3139946528886671</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1290846563163097</v>
+        <v>-0.1290846440590424</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1994498865317438</v>
+        <v>0.1994548436741225</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1089522674104774</v>
+        <v>-0.1089466401285601</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2445675139367825</v>
+        <v>0.2445669171278733</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.06667585479858266</v>
+        <v>-0.06667923000305537</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2084844524534642</v>
+        <v>-0.2084902840114054</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.08668544134255353</v>
+        <v>-0.08667728941889323</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.03570468925691501</v>
+        <v>0.03570522890502753</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.1591338944772778</v>
+        <v>-0.1591272609345905</v>
       </c>
     </row>
     <row r="14">
@@ -1218,55 +1223,55 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1052868472941573</v>
+        <v>0.1052749905785</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1449202013617249</v>
+        <v>0.1449056711565395</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2206497750422585</v>
+        <v>0.2206286299208816</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01880500660357181</v>
+        <v>0.01877999711509601</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.09714522530321366</v>
+        <v>-0.09714803839489827</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.01808750149745618</v>
+        <v>-0.01809581323940824</v>
       </c>
       <c r="H14" t="n">
-        <v>0.06963663455052918</v>
+        <v>0.06963366271904832</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.04784530745402252</v>
+        <v>-0.04784660071458123</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1560413107893932</v>
+        <v>0.1560476141303379</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1801872919912418</v>
+        <v>-0.1801874470417569</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1311758439470698</v>
+        <v>-0.1311790209937747</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.06667585479858266</v>
+        <v>-0.06667923000305537</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.05699540018576835</v>
+        <v>-0.05700855785154003</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3344497916356879</v>
+        <v>-0.3344393227951152</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2736159344099715</v>
+        <v>-0.2736146656061165</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.2391870631180081</v>
+        <v>-0.2391780005920969</v>
       </c>
     </row>
     <row r="15">
@@ -1276,55 +1281,55 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.3025224302472294</v>
+        <v>-0.3025414086752497</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1285168737087633</v>
+        <v>0.1284994890650402</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2191235361737836</v>
+        <v>0.2190993836510087</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08617151389480943</v>
+        <v>0.08614156464175782</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1100201902094372</v>
+        <v>-0.1100246532969607</v>
       </c>
       <c r="G15" t="n">
-        <v>0.09742786136531222</v>
+        <v>0.09742116197334463</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05810370347223572</v>
+        <v>-0.05810826328302209</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1517051060556925</v>
+        <v>0.1517038804515338</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4014707216967044</v>
+        <v>-0.4014672440405158</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2110717045254923</v>
+        <v>-0.211076096741468</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1290069085299771</v>
+        <v>-0.1290135262247127</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2084844524534642</v>
+        <v>-0.2084902840114054</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05699540018576835</v>
+        <v>-0.05700855785154003</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.08575547905589183</v>
+        <v>-0.08574894331630034</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1489680421564213</v>
+        <v>-0.148968088058163</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.2139285579316338</v>
+        <v>-0.2139234564840357</v>
       </c>
     </row>
     <row r="16">
@@ -1334,55 +1339,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1480481308387691</v>
+        <v>-0.1480280602383607</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.228424999538051</v>
+        <v>-0.2284251428394521</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.08859419723550245</v>
+        <v>-0.08859948004689602</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2658783583518063</v>
+        <v>-0.2658841969949202</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.09953736872705168</v>
+        <v>-0.09952899762682288</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.231597346161858</v>
+        <v>-0.2315950880609488</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1083133964638782</v>
+        <v>-0.1083083749550653</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1042482409667988</v>
+        <v>-0.1042472562139691</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01137560382530292</v>
+        <v>0.01139122932632961</v>
       </c>
       <c r="K16" t="n">
-        <v>0.04595707700570791</v>
+        <v>0.04596758191039343</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06537238530367127</v>
+        <v>0.06537804670182855</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.08668544134255353</v>
+        <v>-0.08667728941889323</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3344497916356879</v>
+        <v>-0.3344393227951152</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.08575547905589183</v>
+        <v>-0.08574894331630034</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1497917114034445</v>
+        <v>0.1497967067182525</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.01630201211991701</v>
+        <v>-0.01628519880069524</v>
       </c>
     </row>
     <row r="17">
@@ -1392,55 +1397,55 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01966628653205298</v>
+        <v>-0.01964295660280319</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1666239735273201</v>
+        <v>-0.1666287345046819</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2463175713112158</v>
+        <v>-0.2463249298705208</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1026547546344741</v>
+        <v>-0.102650397078287</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1406992796417736</v>
+        <v>-0.1406890859728792</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.05648179332423926</v>
+        <v>-0.0564805618575122</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1683131366924297</v>
+        <v>-0.1683028290656185</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1779438451389138</v>
+        <v>-0.1779433193663462</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1801940201260942</v>
+        <v>0.1802086516815085</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001108510895196234</v>
+        <v>0.001119136990765943</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1445407681560441</v>
+        <v>0.1445446068592358</v>
       </c>
       <c r="M17" t="n">
-        <v>0.03570468925691501</v>
+        <v>0.03570522890502753</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2736159344099715</v>
+        <v>-0.2736146656061165</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1489680421564213</v>
+        <v>-0.148968088058163</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1497917114034445</v>
+        <v>0.1497967067182525</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.04617973257193433</v>
+        <v>-0.04617028839782494</v>
       </c>
     </row>
     <row r="18">
@@ -1450,52 +1455,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1315149064270793</v>
+        <v>0.1315126204634179</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.2916657504417445</v>
+        <v>-0.2916707537545707</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.153015896914925</v>
+        <v>-0.1530279760886197</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.09448008372799722</v>
+        <v>-0.09448757927052656</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06905742037009066</v>
+        <v>0.06906645850482386</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1526114212996356</v>
+        <v>-0.1526104192842474</v>
       </c>
       <c r="H18" t="n">
-        <v>0.002501461894858713</v>
+        <v>0.002509791409928436</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1208143663468068</v>
+        <v>0.1208124555009644</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.06673731860917852</v>
+        <v>-0.0667163486895082</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.08631534911131751</v>
+        <v>-0.08630211861237901</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.01757525324315103</v>
+        <v>-0.0175686449599894</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1591338944772778</v>
+        <v>-0.1591272609345905</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2391870631180081</v>
+        <v>-0.2391780005920969</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2139285579316338</v>
+        <v>-0.2139234564840357</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.01630201211991701</v>
+        <v>-0.01628519880069524</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.04617973257193433</v>
+        <v>-0.04617028839782494</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
